--- a/in/evd_sdb_sim_parameters.xlsx
+++ b/in/evd_sdb_sim_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fchec\Desktop\evd\sim_ifrc\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C04F4D-6682-4364-B772-57B0B6E3FF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9060211-08EA-448B-A81C-B7907DF47F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>parameter</t>
   </si>
@@ -179,9 +179,6 @@
     <t>number of simulation runs</t>
   </si>
   <si>
-    <t>Varied in simulations. Kept at 0 during the first 14 days of the outbreak.</t>
-  </si>
-  <si>
     <t>Varied in simulations.</t>
   </si>
   <si>
@@ -192,6 +189,12 @@
   </si>
   <si>
     <t xml:space="preserve">Mean DRC health zone population (Ituri, South Kivu, North Kivu provinces only), based on UN-OCHA projections: https://data.humdata.org/dataset/cod-ps-cod </t>
+  </si>
+  <si>
+    <t>Assume 10% higher as source reported hospitalised cases.</t>
+  </si>
+  <si>
+    <t>Preferably go up to 10,000.</t>
   </si>
 </sst>
 </file>
@@ -591,7 +594,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -672,6 +675,9 @@
       <c r="B7" s="4">
         <v>0.5</v>
       </c>
+      <c r="E7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
@@ -712,10 +718,13 @@
         <v>14</v>
       </c>
       <c r="B10" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -723,7 +732,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="4">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>34</v>
@@ -734,24 +743,27 @@
         <v>16</v>
       </c>
       <c r="B12" s="4">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4">
         <v>211121</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
